--- a/reviews/REVIEWED_MorrisRamen_20161002_20191011_20260810_autoPush.xlsx
+++ b/reviews/REVIEWED_MorrisRamen_20161002_20191011_20260810_autoPush.xlsx
@@ -6289,7 +6289,7 @@
         </is>
       </c>
       <c r="H162" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I162" t="inlineStr"/>
     </row>
@@ -6320,7 +6320,7 @@
         </is>
       </c>
       <c r="H163" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I163" t="inlineStr"/>
     </row>
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="H164" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I164" t="inlineStr"/>
     </row>
@@ -6393,7 +6393,7 @@
         </is>
       </c>
       <c r="H165" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I165" t="inlineStr"/>
     </row>
@@ -6429,9 +6429,13 @@
         </is>
       </c>
       <c r="H166" t="b">
-        <v>0</v>
-      </c>
-      <c r="I166" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>PLANNED PARENTHOOD</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -6464,7 +6468,7 @@
         </is>
       </c>
       <c r="H167" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I167" t="inlineStr"/>
     </row>
@@ -6502,9 +6506,13 @@
         </is>
       </c>
       <c r="H168" t="b">
-        <v>0</v>
-      </c>
-      <c r="I168" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>PERSONAL</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -6539,7 +6547,7 @@
         </is>
       </c>
       <c r="H169" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I169" t="inlineStr"/>
     </row>
@@ -6580,7 +6588,7 @@
         </is>
       </c>
       <c r="H170" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I170" t="inlineStr"/>
     </row>
@@ -6617,7 +6625,7 @@
         </is>
       </c>
       <c r="H171" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I171" t="inlineStr"/>
     </row>
@@ -6653,7 +6661,7 @@
         </is>
       </c>
       <c r="H172" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I172" t="inlineStr"/>
     </row>
@@ -6688,7 +6696,7 @@
         </is>
       </c>
       <c r="H173" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I173" t="inlineStr"/>
     </row>
@@ -6723,7 +6731,7 @@
         </is>
       </c>
       <c r="H174" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I174" t="inlineStr"/>
     </row>
@@ -6758,7 +6766,7 @@
         </is>
       </c>
       <c r="H175" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I175" t="inlineStr"/>
     </row>
@@ -6796,9 +6804,13 @@
         </is>
       </c>
       <c r="H176" t="b">
-        <v>0</v>
-      </c>
-      <c r="I176" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>PLANNED PARENTHOOD</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -6832,7 +6844,7 @@
         </is>
       </c>
       <c r="H177" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I177" t="inlineStr"/>
     </row>
@@ -6876,7 +6888,7 @@
         </is>
       </c>
       <c r="H178" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I178" t="inlineStr"/>
     </row>
@@ -6911,7 +6923,7 @@
         </is>
       </c>
       <c r="H179" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I179" t="inlineStr"/>
     </row>
@@ -6949,7 +6961,7 @@
         </is>
       </c>
       <c r="H180" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I180" t="inlineStr"/>
     </row>
@@ -6990,7 +7002,7 @@
         </is>
       </c>
       <c r="H181" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I181" t="inlineStr"/>
     </row>

--- a/reviews/REVIEWED_MorrisRamen_20161002_20191011_20260810_autoPush.xlsx
+++ b/reviews/REVIEWED_MorrisRamen_20161002_20191011_20260810_autoPush.xlsx
@@ -7042,7 +7042,7 @@
         </is>
       </c>
       <c r="H182" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I182" t="inlineStr"/>
     </row>
@@ -7079,7 +7079,7 @@
         </is>
       </c>
       <c r="H183" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I183" t="inlineStr"/>
     </row>
@@ -7116,9 +7116,13 @@
         </is>
       </c>
       <c r="H184" t="b">
-        <v>0</v>
-      </c>
-      <c r="I184" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>PERSONAL</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -7151,9 +7155,13 @@
         </is>
       </c>
       <c r="H185" t="b">
-        <v>0</v>
-      </c>
-      <c r="I185" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Evers</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -7187,7 +7195,7 @@
         </is>
       </c>
       <c r="H186" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I186" t="inlineStr"/>
     </row>
@@ -7223,7 +7231,7 @@
         </is>
       </c>
       <c r="H187" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I187" t="inlineStr"/>
     </row>
@@ -7260,7 +7268,7 @@
         </is>
       </c>
       <c r="H188" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I188" t="inlineStr"/>
     </row>
@@ -7295,7 +7303,7 @@
         </is>
       </c>
       <c r="H189" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I189" t="inlineStr"/>
     </row>
@@ -7331,9 +7339,13 @@
         </is>
       </c>
       <c r="H190" t="b">
-        <v>0</v>
-      </c>
-      <c r="I190" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>PERSONAL</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -7366,7 +7378,7 @@
         </is>
       </c>
       <c r="H191" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I191" t="inlineStr"/>
     </row>
@@ -7405,7 +7417,7 @@
         </is>
       </c>
       <c r="H192" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I192" t="inlineStr"/>
     </row>
@@ -7436,7 +7448,7 @@
         </is>
       </c>
       <c r="H193" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I193" t="inlineStr"/>
     </row>
@@ -7473,7 +7485,7 @@
         </is>
       </c>
       <c r="H194" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I194" t="inlineStr"/>
     </row>
@@ -7509,7 +7521,7 @@
         </is>
       </c>
       <c r="H195" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I195" t="inlineStr"/>
     </row>
@@ -7545,7 +7557,7 @@
         </is>
       </c>
       <c r="H196" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I196" t="inlineStr"/>
     </row>
@@ -7580,7 +7592,7 @@
         </is>
       </c>
       <c r="H197" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I197" t="inlineStr"/>
     </row>
@@ -7615,7 +7627,7 @@
         </is>
       </c>
       <c r="H198" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I198" t="inlineStr"/>
     </row>
@@ -7652,9 +7664,13 @@
         </is>
       </c>
       <c r="H199" t="b">
-        <v>0</v>
-      </c>
-      <c r="I199" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>PERSONAL</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -7687,7 +7703,7 @@
         </is>
       </c>
       <c r="H200" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I200" t="inlineStr"/>
     </row>
@@ -7722,7 +7738,7 @@
         </is>
       </c>
       <c r="H201" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I201" t="inlineStr"/>
     </row>
